--- a/Databases/Expanded_workbook/factory_workbook.xlsx
+++ b/Databases/Expanded_workbook/factory_workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Summer_projects_2026\Factory-SC-optimiser\Databases\Expanded_workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19B7532-76DD-4B99-A9DA-6D7BE0A98319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3E2753-BAC8-47B8-9864-282CE312EA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="215">
   <si>
     <t>Product Code</t>
   </si>
@@ -650,6 +650,48 @@
   </si>
   <si>
     <t>Purchase Order Value</t>
+  </si>
+  <si>
+    <t>Inspection ID</t>
+  </si>
+  <si>
+    <t>Quantity Inspected</t>
+  </si>
+  <si>
+    <t>Quantity Passed</t>
+  </si>
+  <si>
+    <t>Quantity Failed</t>
+  </si>
+  <si>
+    <t>Defect Type</t>
+  </si>
+  <si>
+    <t>Defect Rate %</t>
+  </si>
+  <si>
+    <t>Corrective Action</t>
+  </si>
+  <si>
+    <t>QC-001</t>
+  </si>
+  <si>
+    <t>Scratched finish</t>
+  </si>
+  <si>
+    <t>Rework</t>
+  </si>
+  <si>
+    <t>QC-002</t>
+  </si>
+  <si>
+    <t>Welding defect</t>
+  </si>
+  <si>
+    <t>QC-003</t>
+  </si>
+  <si>
+    <t>Paint defect</t>
   </si>
 </sst>
 </file>
@@ -1115,9 +1157,165 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4EB8859-761D-4D55-8400-EEC432FE2021}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1" t="s">
+        <v>204</v>
+      </c>
+      <c r="I1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>96</v>
+      </c>
+      <c r="G2">
+        <v>94</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J2">
+        <f>IFERROR(H2/F2,0)</f>
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>169</v>
+      </c>
+      <c r="L2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>48</v>
+      </c>
+      <c r="G3">
+        <v>47</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J3">
+        <f>IFERROR(H3/F3,0)</f>
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>169</v>
+      </c>
+      <c r="L3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>152</v>
+      </c>
+      <c r="G4">
+        <v>149</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J4">
+        <f>IFERROR(H4/F4,0)</f>
+        <v>1.9736842105263157E-2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>169</v>
+      </c>
+      <c r="L4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
